--- a/Datos limpios/Pricing diario/2025/Trigo.xlsx
+++ b/Datos limpios/Pricing diario/2025/Trigo.xlsx
@@ -10522,298 +10522,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D6CA5EAACE9DA04D9E421A617A76D009" ma:contentTypeVersion="19" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="854b0670eee28d8fa271d4f22cb9c97d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77131357-5c03-45fa-a80b-b9111bb46cb1" xmlns:ns3="d3f11db4-a96c-41b4-b8ec-902c72f52048" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b486ba09ce8a2fb19cc660d7edf32df4" ns2:_="" ns3:_="">
-    <xsd:import namespace="77131357-5c03-45fa-a80b-b9111bb46cb1"/>
-    <xsd:import namespace="d3f11db4-a96c-41b4-b8ec-902c72f52048"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="77131357-5c03-45fa-a80b-b9111bb46cb1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_Flow_SignoffStatus" ma:index="20" nillable="true" ma:displayName="Estado de aprobación" ma:internalName="Estado_x0020_de_x0020_aprobaci_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6ab20cb4-9c0f-41d2-89f3-02c382a657d6" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="25" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="26" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d3f11db4-a96c-41b4-b8ec-902c72f52048" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="24" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ac6aff7b-77d9-4645-af3f-7b0008d975fa}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d3f11db4-a96c-41b4-b8ec-902c72f52048">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1" xsi:nil="true"/>
-    <TaxCatchAll xmlns="d3f11db4-a96c-41b4-b8ec-902c72f52048" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE1D493C-B089-4F4B-8FEA-24F7118E7DE0}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56BF83E2-1D65-4B23-A619-370A32696EA5}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0365C15F-9354-401D-9E91-8918896E46BF}"/>
 </file>
--- a/Datos limpios/Pricing diario/2025/Trigo.xlsx
+++ b/Datos limpios/Pricing diario/2025/Trigo.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K274"/>
+  <dimension ref="A1:K297"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -8785,16 +8785,16 @@
         <v>45909</v>
       </c>
       <c r="B228">
-        <v>64232.93</v>
+        <v>63632.93</v>
       </c>
       <c r="C228">
-        <v>31.7</v>
+        <v>491.02</v>
       </c>
       <c r="D228">
         <v>3067.26</v>
       </c>
       <c r="E228">
-        <v>61197.37</v>
+        <v>61056.69</v>
       </c>
       <c r="F228">
         <v>12578.03</v>
@@ -8809,7 +8809,7 @@
         <v>12485.51</v>
       </c>
       <c r="J228">
-        <v>73682.87999999999</v>
+        <v>73542.2</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -9081,16 +9081,16 @@
         <v>45917</v>
       </c>
       <c r="B236">
-        <v>137834.57</v>
+        <v>137738.57</v>
       </c>
       <c r="C236">
-        <v>310</v>
+        <v>372.08</v>
       </c>
       <c r="D236">
         <v>1580.61</v>
       </c>
       <c r="E236">
-        <v>136563.96</v>
+        <v>136530.04</v>
       </c>
       <c r="F236">
         <v>27514.66</v>
@@ -9105,7 +9105,7 @@
         <v>27630.52</v>
       </c>
       <c r="J236">
-        <v>164194.48</v>
+        <v>164160.56</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -9303,16 +9303,16 @@
         <v>45923</v>
       </c>
       <c r="B242">
-        <v>141286.59</v>
+        <v>140286.59</v>
       </c>
       <c r="C242">
-        <v>5036</v>
+        <v>5848.27</v>
       </c>
       <c r="D242">
         <v>299.14</v>
       </c>
       <c r="E242">
-        <v>146023.45</v>
+        <v>145835.72</v>
       </c>
       <c r="F242">
         <v>16622.81</v>
@@ -9327,7 +9327,7 @@
         <v>16622.81</v>
       </c>
       <c r="J242">
-        <v>162646.26</v>
+        <v>162458.53</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -9340,16 +9340,16 @@
         <v>45924</v>
       </c>
       <c r="B243">
-        <v>149305.62</v>
+        <v>148805.62</v>
       </c>
       <c r="C243">
         <v>420</v>
       </c>
       <c r="D243">
-        <v>3470</v>
+        <v>3970</v>
       </c>
       <c r="E243">
-        <v>146255.62</v>
+        <v>145255.62</v>
       </c>
       <c r="F243">
         <v>14783.58</v>
@@ -9364,7 +9364,7 @@
         <v>14843.58</v>
       </c>
       <c r="J243">
-        <v>161099.2</v>
+        <v>160099.2</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -9599,16 +9599,16 @@
         <v>45931</v>
       </c>
       <c r="B250">
-        <v>52864.42</v>
+        <v>47864.42</v>
       </c>
       <c r="C250">
-        <v>506.2</v>
+        <v>5384.71</v>
       </c>
       <c r="D250">
         <v>0</v>
       </c>
       <c r="E250">
-        <v>53370.62</v>
+        <v>53249.13</v>
       </c>
       <c r="F250">
         <v>6546.9</v>
@@ -9623,7 +9623,7 @@
         <v>6546.9</v>
       </c>
       <c r="J250">
-        <v>59917.52</v>
+        <v>59796.03</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
@@ -9676,13 +9676,13 @@
         <v>59908.66</v>
       </c>
       <c r="C252">
-        <v>4795.139999999999</v>
+        <v>4505.05</v>
       </c>
       <c r="D252">
         <v>0</v>
       </c>
       <c r="E252">
-        <v>64703.8</v>
+        <v>64413.71000000001</v>
       </c>
       <c r="F252">
         <v>5524.38</v>
@@ -9697,7 +9697,7 @@
         <v>5524.38</v>
       </c>
       <c r="J252">
-        <v>70228.18000000001</v>
+        <v>69938.09000000001</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
@@ -9821,16 +9821,16 @@
         <v>45937</v>
       </c>
       <c r="B256">
-        <v>79915.69</v>
+        <v>79715.69</v>
       </c>
       <c r="C256">
-        <v>1400</v>
+        <v>1444.73</v>
       </c>
       <c r="D256">
         <v>1063.12</v>
       </c>
       <c r="E256">
-        <v>80252.57000000001</v>
+        <v>80097.3</v>
       </c>
       <c r="F256">
         <v>7513.22</v>
@@ -9845,7 +9845,7 @@
         <v>7513.22</v>
       </c>
       <c r="J256">
-        <v>87765.79000000001</v>
+        <v>87610.52</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
@@ -10043,16 +10043,16 @@
         <v>45943</v>
       </c>
       <c r="B262">
-        <v>130553.83</v>
+        <v>128553.83</v>
       </c>
       <c r="C262">
-        <v>4259.09</v>
+        <v>5962.53</v>
       </c>
       <c r="D262">
         <v>920</v>
       </c>
       <c r="E262">
-        <v>133892.92</v>
+        <v>133596.36</v>
       </c>
       <c r="F262">
         <v>3140.11</v>
@@ -10067,7 +10067,7 @@
         <v>3240.11</v>
       </c>
       <c r="J262">
-        <v>137133.03</v>
+        <v>136836.47</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
@@ -10487,33 +10487,884 @@
         <v>45957</v>
       </c>
       <c r="B274">
-        <v>960</v>
+        <v>49420.54</v>
       </c>
       <c r="C274">
-        <v>0</v>
+        <v>890.6799999999999</v>
       </c>
       <c r="D274">
-        <v>0</v>
+        <v>2897.97</v>
       </c>
       <c r="E274">
-        <v>960</v>
+        <v>47413.25</v>
       </c>
       <c r="F274">
-        <v>0</v>
+        <v>5262.29</v>
       </c>
       <c r="G274">
         <v>0</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I274">
-        <v>0</v>
+        <v>3262.29</v>
       </c>
       <c r="J274">
-        <v>960</v>
+        <v>50675.54</v>
       </c>
       <c r="K274" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B275">
+        <v>87911.69</v>
+      </c>
+      <c r="C275">
+        <v>1599.02</v>
+      </c>
+      <c r="D275">
+        <v>760</v>
+      </c>
+      <c r="E275">
+        <v>88750.71000000001</v>
+      </c>
+      <c r="F275">
+        <v>13606.05</v>
+      </c>
+      <c r="G275">
+        <v>0</v>
+      </c>
+      <c r="H275">
+        <v>0</v>
+      </c>
+      <c r="I275">
+        <v>13606.05</v>
+      </c>
+      <c r="J275">
+        <v>102356.76</v>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B276">
+        <v>59342.82</v>
+      </c>
+      <c r="C276">
+        <v>528.65</v>
+      </c>
+      <c r="D276">
+        <v>1713.64</v>
+      </c>
+      <c r="E276">
+        <v>58157.83</v>
+      </c>
+      <c r="F276">
+        <v>4309.37</v>
+      </c>
+      <c r="G276">
+        <v>0</v>
+      </c>
+      <c r="H276">
+        <v>25</v>
+      </c>
+      <c r="I276">
+        <v>4284.37</v>
+      </c>
+      <c r="J276">
+        <v>62442.2</v>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B277">
+        <v>82516.25</v>
+      </c>
+      <c r="C277">
+        <v>1304.92</v>
+      </c>
+      <c r="D277">
+        <v>360</v>
+      </c>
+      <c r="E277">
+        <v>83461.17</v>
+      </c>
+      <c r="F277">
+        <v>8736.530000000001</v>
+      </c>
+      <c r="G277">
+        <v>0</v>
+      </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
+      <c r="I277">
+        <v>8736.530000000001</v>
+      </c>
+      <c r="J277">
+        <v>92197.7</v>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B278">
+        <v>78970.52</v>
+      </c>
+      <c r="C278">
+        <v>982.49</v>
+      </c>
+      <c r="D278">
+        <v>35.68</v>
+      </c>
+      <c r="E278">
+        <v>79917.33000000002</v>
+      </c>
+      <c r="F278">
+        <v>10351.99</v>
+      </c>
+      <c r="G278">
+        <v>404.46</v>
+      </c>
+      <c r="H278">
+        <v>111.56</v>
+      </c>
+      <c r="I278">
+        <v>10644.89</v>
+      </c>
+      <c r="J278">
+        <v>90562.22000000002</v>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B279">
+        <v>606.17</v>
+      </c>
+      <c r="C279">
+        <v>60</v>
+      </c>
+      <c r="D279">
+        <v>0</v>
+      </c>
+      <c r="E279">
+        <v>666.17</v>
+      </c>
+      <c r="F279">
+        <v>931.64</v>
+      </c>
+      <c r="G279">
+        <v>0</v>
+      </c>
+      <c r="H279">
+        <v>0</v>
+      </c>
+      <c r="I279">
+        <v>931.64</v>
+      </c>
+      <c r="J279">
+        <v>1597.81</v>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2">
+        <v>45963</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+      <c r="E280">
+        <v>0</v>
+      </c>
+      <c r="F280">
+        <v>0</v>
+      </c>
+      <c r="G280">
+        <v>0</v>
+      </c>
+      <c r="H280">
+        <v>0</v>
+      </c>
+      <c r="I280">
+        <v>0</v>
+      </c>
+      <c r="J280">
+        <v>0</v>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B281">
+        <v>90137.72</v>
+      </c>
+      <c r="C281">
+        <v>390</v>
+      </c>
+      <c r="D281">
+        <v>2220</v>
+      </c>
+      <c r="E281">
+        <v>88307.72</v>
+      </c>
+      <c r="F281">
+        <v>11145.39</v>
+      </c>
+      <c r="G281">
+        <v>0</v>
+      </c>
+      <c r="H281">
+        <v>0</v>
+      </c>
+      <c r="I281">
+        <v>11145.39</v>
+      </c>
+      <c r="J281">
+        <v>99453.11</v>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B282">
+        <v>67599.42999999999</v>
+      </c>
+      <c r="C282">
+        <v>5514.29</v>
+      </c>
+      <c r="D282">
+        <v>886</v>
+      </c>
+      <c r="E282">
+        <v>72227.71999999999</v>
+      </c>
+      <c r="F282">
+        <v>5552.6</v>
+      </c>
+      <c r="G282">
+        <v>0</v>
+      </c>
+      <c r="H282">
+        <v>180</v>
+      </c>
+      <c r="I282">
+        <v>5372.6</v>
+      </c>
+      <c r="J282">
+        <v>77600.31999999999</v>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B283">
+        <v>85270.99000000001</v>
+      </c>
+      <c r="C283">
+        <v>1550.75</v>
+      </c>
+      <c r="D283">
+        <v>1401</v>
+      </c>
+      <c r="E283">
+        <v>85420.74000000001</v>
+      </c>
+      <c r="F283">
+        <v>9871.959999999999</v>
+      </c>
+      <c r="G283">
+        <v>0</v>
+      </c>
+      <c r="H283">
+        <v>0</v>
+      </c>
+      <c r="I283">
+        <v>9871.959999999999</v>
+      </c>
+      <c r="J283">
+        <v>95292.70000000001</v>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B284">
+        <v>62794.73</v>
+      </c>
+      <c r="C284">
+        <v>1541.4</v>
+      </c>
+      <c r="D284">
+        <v>570</v>
+      </c>
+      <c r="E284">
+        <v>63766.13</v>
+      </c>
+      <c r="F284">
+        <v>7686.5</v>
+      </c>
+      <c r="G284">
+        <v>0</v>
+      </c>
+      <c r="H284">
+        <v>300</v>
+      </c>
+      <c r="I284">
+        <v>7386.5</v>
+      </c>
+      <c r="J284">
+        <v>71152.63</v>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B285">
+        <v>53014.63</v>
+      </c>
+      <c r="C285">
+        <v>1106.03</v>
+      </c>
+      <c r="D285">
+        <v>1066.87</v>
+      </c>
+      <c r="E285">
+        <v>53053.78999999999</v>
+      </c>
+      <c r="F285">
+        <v>8720.52</v>
+      </c>
+      <c r="G285">
+        <v>0</v>
+      </c>
+      <c r="H285">
+        <v>0</v>
+      </c>
+      <c r="I285">
+        <v>8720.52</v>
+      </c>
+      <c r="J285">
+        <v>61774.31</v>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2">
+        <v>45969</v>
+      </c>
+      <c r="B286">
+        <v>254.2</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286">
+        <v>254.2</v>
+      </c>
+      <c r="F286">
+        <v>0</v>
+      </c>
+      <c r="G286">
+        <v>0</v>
+      </c>
+      <c r="H286">
+        <v>0</v>
+      </c>
+      <c r="I286">
+        <v>0</v>
+      </c>
+      <c r="J286">
+        <v>254.2</v>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B287">
+        <v>84866.06</v>
+      </c>
+      <c r="C287">
+        <v>812</v>
+      </c>
+      <c r="D287">
+        <v>2178.62</v>
+      </c>
+      <c r="E287">
+        <v>83499.44</v>
+      </c>
+      <c r="F287">
+        <v>9012.540000000001</v>
+      </c>
+      <c r="G287">
+        <v>0</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+      <c r="I287">
+        <v>9012.540000000001</v>
+      </c>
+      <c r="J287">
+        <v>92511.98000000001</v>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B288">
+        <v>84067.49000000001</v>
+      </c>
+      <c r="C288">
+        <v>881.8</v>
+      </c>
+      <c r="D288">
+        <v>210</v>
+      </c>
+      <c r="E288">
+        <v>84739.29000000001</v>
+      </c>
+      <c r="F288">
+        <v>7972.79</v>
+      </c>
+      <c r="G288">
+        <v>0</v>
+      </c>
+      <c r="H288">
+        <v>0</v>
+      </c>
+      <c r="I288">
+        <v>7972.79</v>
+      </c>
+      <c r="J288">
+        <v>92712.08</v>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B289">
+        <v>103835.3</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>1226.97</v>
+      </c>
+      <c r="E289">
+        <v>102608.33</v>
+      </c>
+      <c r="F289">
+        <v>7339.21</v>
+      </c>
+      <c r="G289">
+        <v>0</v>
+      </c>
+      <c r="H289">
+        <v>0</v>
+      </c>
+      <c r="I289">
+        <v>7339.21</v>
+      </c>
+      <c r="J289">
+        <v>109947.54</v>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B290">
+        <v>132336.4</v>
+      </c>
+      <c r="C290">
+        <v>774.08</v>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+      <c r="E290">
+        <v>133110.48</v>
+      </c>
+      <c r="F290">
+        <v>12247.26</v>
+      </c>
+      <c r="G290">
+        <v>388.53</v>
+      </c>
+      <c r="H290">
+        <v>0</v>
+      </c>
+      <c r="I290">
+        <v>12635.79</v>
+      </c>
+      <c r="J290">
+        <v>145746.27</v>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B291">
+        <v>136705.2</v>
+      </c>
+      <c r="C291">
+        <v>710.8099999999999</v>
+      </c>
+      <c r="D291">
+        <v>4256</v>
+      </c>
+      <c r="E291">
+        <v>133160.01</v>
+      </c>
+      <c r="F291">
+        <v>26154.16</v>
+      </c>
+      <c r="G291">
+        <v>0</v>
+      </c>
+      <c r="H291">
+        <v>0</v>
+      </c>
+      <c r="I291">
+        <v>26154.16</v>
+      </c>
+      <c r="J291">
+        <v>159314.17</v>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2">
+        <v>45976</v>
+      </c>
+      <c r="B292">
+        <v>720</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>0</v>
+      </c>
+      <c r="E292">
+        <v>720</v>
+      </c>
+      <c r="F292">
+        <v>0</v>
+      </c>
+      <c r="G292">
+        <v>0</v>
+      </c>
+      <c r="H292">
+        <v>0</v>
+      </c>
+      <c r="I292">
+        <v>0</v>
+      </c>
+      <c r="J292">
+        <v>720</v>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B293">
+        <v>102306.82</v>
+      </c>
+      <c r="C293">
+        <v>665.03</v>
+      </c>
+      <c r="D293">
+        <v>440</v>
+      </c>
+      <c r="E293">
+        <v>102531.85</v>
+      </c>
+      <c r="F293">
+        <v>10884.48</v>
+      </c>
+      <c r="G293">
+        <v>0</v>
+      </c>
+      <c r="H293">
+        <v>0</v>
+      </c>
+      <c r="I293">
+        <v>10884.48</v>
+      </c>
+      <c r="J293">
+        <v>113416.33</v>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B294">
+        <v>109614.54</v>
+      </c>
+      <c r="C294">
+        <v>1716.92</v>
+      </c>
+      <c r="D294">
+        <v>590</v>
+      </c>
+      <c r="E294">
+        <v>110741.46</v>
+      </c>
+      <c r="F294">
+        <v>5898.33</v>
+      </c>
+      <c r="G294">
+        <v>0</v>
+      </c>
+      <c r="H294">
+        <v>120</v>
+      </c>
+      <c r="I294">
+        <v>5778.33</v>
+      </c>
+      <c r="J294">
+        <v>116519.79</v>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B295">
+        <v>123958.86</v>
+      </c>
+      <c r="C295">
+        <v>1103.01</v>
+      </c>
+      <c r="D295">
+        <v>6364</v>
+      </c>
+      <c r="E295">
+        <v>118697.87</v>
+      </c>
+      <c r="F295">
+        <v>17568.67</v>
+      </c>
+      <c r="G295">
+        <v>0</v>
+      </c>
+      <c r="H295">
+        <v>0</v>
+      </c>
+      <c r="I295">
+        <v>17568.67</v>
+      </c>
+      <c r="J295">
+        <v>136266.54</v>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B296">
+        <v>93866.78</v>
+      </c>
+      <c r="C296">
+        <v>2046.14</v>
+      </c>
+      <c r="D296">
+        <v>60</v>
+      </c>
+      <c r="E296">
+        <v>95852.92</v>
+      </c>
+      <c r="F296">
+        <v>4646.53</v>
+      </c>
+      <c r="G296">
+        <v>249.67</v>
+      </c>
+      <c r="H296">
+        <v>0</v>
+      </c>
+      <c r="I296">
+        <v>4896.2</v>
+      </c>
+      <c r="J296">
+        <v>100749.12</v>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B297">
+        <v>19756.07</v>
+      </c>
+      <c r="C297">
+        <v>567</v>
+      </c>
+      <c r="D297">
+        <v>0</v>
+      </c>
+      <c r="E297">
+        <v>20323.07</v>
+      </c>
+      <c r="F297">
+        <v>278.3</v>
+      </c>
+      <c r="G297">
+        <v>0</v>
+      </c>
+      <c r="H297">
+        <v>210</v>
+      </c>
+      <c r="I297">
+        <v>68.30000000000001</v>
+      </c>
+      <c r="J297">
+        <v>20391.37</v>
+      </c>
+      <c r="K297" t="inlineStr">
         <is>
           <t>TRIGO</t>
         </is>
